--- a/missing-payments.xlsx
+++ b/missing-payments.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42BE6AA-57EA-406F-9998-F8ABBB3E7A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1A9889-ABA9-4E25-84DE-452A6142AAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -756,7 +756,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -829,12 +829,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF843C0C"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF1F497D"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -853,7 +847,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -861,14 +855,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -916,12 +910,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -941,12 +929,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -961,25 +948,19 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="20% - Accent6" xfId="2" builtinId="50"/>
+  <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1417,7 +1398,7 @@
       <c r="D3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>240</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -1452,7 +1433,7 @@
       <c r="D4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>240</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -1487,7 +1468,7 @@
       <c r="D5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>240</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -1522,7 +1503,7 @@
       <c r="D6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>240</v>
       </c>
       <c r="F6" s="9" t="s">
@@ -1557,7 +1538,7 @@
       <c r="D7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>240</v>
       </c>
       <c r="F7" s="9" t="s">
@@ -1592,7 +1573,7 @@
       <c r="D8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="12" t="s">
         <v>240</v>
       </c>
       <c r="F8" s="9" t="s">
@@ -1627,7 +1608,7 @@
       <c r="D9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="12" t="s">
         <v>240</v>
       </c>
       <c r="F9" s="9" t="s">
@@ -1662,7 +1643,7 @@
       <c r="D10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="12" t="s">
         <v>240</v>
       </c>
       <c r="F10" s="9" t="s">
@@ -1697,7 +1678,7 @@
       <c r="D11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="12" t="s">
         <v>240</v>
       </c>
       <c r="F11" s="9" t="s">
@@ -1732,7 +1713,7 @@
       <c r="D12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="12" t="s">
         <v>240</v>
       </c>
       <c r="F12" s="9" t="s">
@@ -1767,7 +1748,7 @@
       <c r="D13" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>240</v>
       </c>
       <c r="F13" s="9" t="s">
@@ -1790,1048 +1771,1058 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="12">
         <v>200</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="10" t="s">
+      <c r="F14" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="12" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="12">
         <v>200</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="10" t="s">
+      <c r="F15" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="12" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="12">
         <v>200</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="10" t="s">
+      <c r="F16" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="12" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="12">
         <v>200</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="F17" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="12" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="12">
         <v>50</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="10" t="s">
+      <c r="F18" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="J18" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="12" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="12">
         <v>50</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="10" t="s">
+      <c r="F19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="J19" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19" s="12" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="12">
         <v>50</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="10" t="s">
+      <c r="F20" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="J20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="K20" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="12">
         <v>50</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="10" t="s">
+      <c r="F21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="I21" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="J21" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="K21" s="12" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="12">
         <v>150</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="10" t="s">
+      <c r="F22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="J22" s="14" t="s">
+      <c r="J22" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="K22" s="12" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>100</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11" t="s">
+      <c r="E23" s="10"/>
+      <c r="F23" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="J23" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="K23" s="10" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <v>50</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="10"/>
+      <c r="F24" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K24" s="10" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>50</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11" t="s">
+      <c r="E25" s="10"/>
+      <c r="F25" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="J25" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="10" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="10">
         <v>50</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11" t="s">
+      <c r="E26" s="10"/>
+      <c r="F26" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="J26" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="K26" s="10" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <v>50</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11" t="s">
+      <c r="E27" s="10"/>
+      <c r="F27" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="K27" s="10" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="10">
         <v>100</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11" t="s">
+      <c r="E28" s="10"/>
+      <c r="F28" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="J28" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="K28" s="10" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="11">
         <v>1</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="12" t="s">
+      <c r="F29" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="I29" s="12" t="s">
+      <c r="I29" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="J29" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K29" s="12" t="s">
+      <c r="K29" s="11" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <v>2</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" s="12" t="s">
+      <c r="F30" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="H30" s="12" t="s">
+      <c r="H30" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="I30" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J30" s="12" t="s">
+      <c r="J30" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="K30" s="12" t="s">
+      <c r="K30" s="11" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="11">
         <v>1</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F31" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="12" t="s">
+      <c r="F31" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="I31" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J31" s="12" t="s">
+      <c r="J31" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K31" s="12" t="s">
+      <c r="K31" s="11" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <v>1</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F32" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="12" t="s">
+      <c r="F32" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J32" s="12" t="s">
+      <c r="J32" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K32" s="12" t="s">
+      <c r="K32" s="11" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <v>1</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F33" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="12" t="s">
+      <c r="F33" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="H33" s="12" t="s">
+      <c r="H33" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="I33" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J33" s="12" t="s">
+      <c r="J33" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K33" s="12" t="s">
+      <c r="K33" s="11" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="11">
         <v>1</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F34" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="12" t="s">
+      <c r="F34" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="I34" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J34" s="12" t="s">
+      <c r="J34" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K34" s="12" t="s">
+      <c r="K34" s="11" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="11">
         <v>1</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="12" t="s">
+      <c r="F35" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="I35" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J35" s="12" t="s">
+      <c r="J35" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K35" s="12" t="s">
+      <c r="K35" s="11" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="11">
         <v>1</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" s="12" t="s">
+      <c r="F36" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="I36" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J36" s="12" t="s">
+      <c r="J36" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K36" s="12" t="s">
+      <c r="K36" s="11" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="11">
         <v>1</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="12" t="s">
+      <c r="F37" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H37" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J37" s="12" t="s">
+      <c r="J37" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K37" s="12" t="s">
+      <c r="K37" s="11" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="11">
         <v>1</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F38" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="12" t="s">
+      <c r="F38" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="H38" s="12" t="s">
+      <c r="H38" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="I38" s="12" t="s">
+      <c r="I38" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J38" s="12" t="s">
+      <c r="J38" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K38" s="12" t="s">
+      <c r="K38" s="11" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="11">
         <v>1</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F39" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39" s="12" t="s">
+      <c r="F39" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="H39" s="12" t="s">
+      <c r="H39" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="I39" s="12" t="s">
+      <c r="I39" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J39" s="12" t="s">
+      <c r="J39" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K39" s="12" t="s">
+      <c r="K39" s="11" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="11">
         <v>1</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" s="12" t="s">
+      <c r="F40" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="H40" s="12" t="s">
+      <c r="H40" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="I40" s="12" t="s">
+      <c r="I40" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J40" s="12" t="s">
+      <c r="J40" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K40" s="12" t="s">
+      <c r="K40" s="11" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="11">
         <v>1</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E41" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" s="12" t="s">
+      <c r="F41" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H41" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="I41" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J41" s="12" t="s">
+      <c r="J41" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K41" s="12" t="s">
+      <c r="K41" s="11" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="11">
         <v>1</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F42" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="12" t="s">
+      <c r="F42" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="H42" s="12" t="s">
+      <c r="H42" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="I42" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J42" s="12" t="s">
+      <c r="J42" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K42" s="12" t="s">
+      <c r="K42" s="11" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="B43" s="12">
+      <c r="B43" s="11">
         <v>1</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="F43" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="12" t="s">
+      <c r="F43" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="H43" s="12" t="s">
+      <c r="H43" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="I43" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="J43" s="12" t="s">
+      <c r="J43" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="K43" s="12" t="s">
+      <c r="K43" s="11" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B44" s="15">
+    <row r="44" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A44" s="13"/>
+      <c r="B44" s="14">
         <f>SUM(B2:B43)</f>
         <v>3516</v>
       </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
